--- a/artfynd/A 39924-2019 artfynd.xlsx
+++ b/artfynd/A 39924-2019 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>117170553</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
